--- a/AAII_Financials/Yearly/NMR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NMR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>NMR</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13633000</v>
+      </c>
+      <c r="E8" s="3">
         <v>12637800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10326900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10046900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11231500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12738600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11949900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10015100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14198700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11562600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12664800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16467900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16779700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18906700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16739900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2957700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2701000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2343400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2473200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2384200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2625600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2569100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2251600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2680200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2105000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2406500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2784300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2516900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2420800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2855700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10675200</v>
+      </c>
+      <c r="E10" s="3">
         <v>9936800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7983500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7573700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8847300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10113000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9380800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7763500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11518500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9457500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10258300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13683600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14262800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16485900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13884200</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,38 +998,41 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>12800</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>521600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>802800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>40800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>93400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1028,41 +1047,44 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>4485900</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>429400</v>
+      </c>
+      <c r="E15" s="3">
         <v>428800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>421900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>474000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>504300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>577300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>590900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>545300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>705300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9486100</v>
+        <v>10205800</v>
       </c>
       <c r="E17" s="3">
+        <v>9473300</v>
+      </c>
+      <c r="F17" s="3">
         <v>8516400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8922500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8843700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9786800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9620400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10325100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11005200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9386900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11450800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13510100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13467300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16745700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15971900</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3151700</v>
+        <v>3427200</v>
       </c>
       <c r="E18" s="3">
+        <v>3164500</v>
+      </c>
+      <c r="F18" s="3">
         <v>1810500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1124400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2387800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2951800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2329400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-310000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3193400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2175600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1213900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2957900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3312400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2161000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>768000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +1244,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1229,21 +1262,21 @@
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>63300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-18600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-63200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>103600</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1259,57 +1292,63 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3580500</v>
+        <v>3856500</v>
       </c>
       <c r="E21" s="3">
+        <v>3593300</v>
+      </c>
+      <c r="F21" s="3">
         <v>2232400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1598400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2892100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3465800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2938900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>298500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3795100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2655800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1791900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3638600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4043500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2994500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1678200</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1337,8 +1376,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1355,105 +1394,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3395000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3151700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1810500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1124400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1866200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2085700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2307200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-340200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3089900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2175600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1213900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2957900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3312400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2161000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>768000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1040500</v>
+      </c>
+      <c r="E24" s="3">
         <v>832800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>638900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>434800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>659500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>635400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>268500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>514500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>978000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>540700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>166100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1030300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1329700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1200200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>532500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2354500</v>
+      </c>
+      <c r="E26" s="3">
         <v>2318900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1171700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>689600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1206700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1450300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2038700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-854700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2111900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1634900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1047800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1927600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1982700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>960700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>235500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2277500</v>
+      </c>
+      <c r="E27" s="3">
         <v>2275400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1096600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>698000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1177600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1384400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2016700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-906400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2065300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1615000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>966900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1917400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1956500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>974800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>104700</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,9 +1853,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1805,21 +1874,21 @@
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-63300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>18600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>63200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-103600</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1835,57 +1904,63 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2277500</v>
+      </c>
+      <c r="E33" s="3">
         <v>2275400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1096600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>698000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1177600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1384400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2016700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-906400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2065300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1615000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>966900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1917400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1956500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>974800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>104700</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2277500</v>
+      </c>
+      <c r="E35" s="3">
         <v>2275400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1096600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>698000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1177600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1384400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2016700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-906400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2065300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1615000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>966900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1917400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1956500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>974800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>104700</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,86 +2158,90 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>27035000</v>
+      </c>
+      <c r="E41" s="3">
         <v>29546100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28027900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28741200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>27309000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31734000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29663800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24245600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22170700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18498800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26995800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14019600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16977800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12571500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15584800</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>210173600</v>
+      </c>
+      <c r="E42" s="3">
         <v>219151100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>224865300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>227649000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>229675100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>239602500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>258377900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>241384100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>244836300</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2168,57 +2257,63 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>60015800</v>
+      </c>
+      <c r="E43" s="3">
         <v>49742500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45180100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>39171300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>41180400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>37454700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47554100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35033300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>36487900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8243300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10032500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12695300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11391800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9592900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>77614600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2246,8 +2341,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2264,87 +2359,93 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>62349500</v>
+        <v>73231900</v>
       </c>
       <c r="E45" s="3">
+        <v>62351300</v>
+      </c>
+      <c r="F45" s="3">
         <v>49327100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45777900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41020900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>53065400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>52434100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>49676500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>54767300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
+      <c r="N45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
       <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2452000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>360789200</v>
+        <v>370456200</v>
       </c>
       <c r="E46" s="3">
+        <v>360791000</v>
+      </c>
+      <c r="F46" s="3">
         <v>347400300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>341339300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>339185400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>361856600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>388029900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>350339500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>358262200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2360,153 +2461,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10254100</v>
+        <v>12542600</v>
       </c>
       <c r="E47" s="3">
-        <v>8656800</v>
+        <v>10204300</v>
       </c>
       <c r="F47" s="3">
+        <v>8611000</v>
+      </c>
+      <c r="G47" s="3">
         <v>8890300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10684800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8875500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9102900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11194100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11816500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>254983000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>256844000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>318383000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>359666000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>310914000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>204682000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3420300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2914600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2967100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3492800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3450800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4199400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4093900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3152800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3191800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2357000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2613000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3421100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3745700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3892700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9455400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1983500</v>
+      </c>
+      <c r="E49" s="3">
         <v>489800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>253800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>272300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>247100</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>178600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>936400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>706500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>812400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1053300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1054700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4702300</v>
+        <v>5321900</v>
       </c>
       <c r="E52" s="3">
-        <v>5159200</v>
+        <v>4750300</v>
       </c>
       <c r="F52" s="3">
+        <v>5205000</v>
+      </c>
+      <c r="G52" s="3">
         <v>5199800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3799600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9488600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7685900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4726200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5509800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1752300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2154100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4124200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3277900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>393987100</v>
+      </c>
+      <c r="E54" s="3">
         <v>379318400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>364597600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>359364800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>357495900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>384420100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>408912600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>369726900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>379868600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>288823000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>302013000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>356411000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>398646000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>344897000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>322704000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,38 +2914,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31639200</v>
+      </c>
+      <c r="E57" s="3">
         <v>27668700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27330800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23767700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26019800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29190600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29004400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21436900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22751400</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -2832,135 +2962,144 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>142903200</v>
+        <v>137756200</v>
       </c>
       <c r="E58" s="3">
+        <v>142584400</v>
+      </c>
+      <c r="F58" s="3">
         <v>145483400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>141364700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>138833000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>159554500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>191505400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>161744000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>167232000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>139767000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>139762000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>141545000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>165007000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>149198000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>124016000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>64196600</v>
+        <v>66669200</v>
       </c>
       <c r="E59" s="3">
-        <v>60372700</v>
+        <v>63341400</v>
       </c>
       <c r="F59" s="3">
+        <v>59808700</v>
+      </c>
+      <c r="G59" s="3">
         <v>64627700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>66038100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>72681800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>62765100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>66931800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>70647500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23217200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20334000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24408600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21872300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12195800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13855800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>238353400</v>
+        <v>240470700</v>
       </c>
       <c r="E60" s="3">
-        <v>236991800</v>
+        <v>237274500</v>
       </c>
       <c r="F60" s="3">
+        <v>236427800</v>
+      </c>
+      <c r="G60" s="3">
         <v>233367100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>234658500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>265269300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>286960200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>253735200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>264853100</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2976,87 +3115,93 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>92779100</v>
+        <v>100853800</v>
       </c>
       <c r="E61" s="3">
+        <v>93097900</v>
+      </c>
+      <c r="F61" s="3">
         <v>86179900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>82201800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>81136500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>77143400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>78933300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>75210500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>73406400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48497000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>59752300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>71108600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>75359900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>69014600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>76883800</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27496000</v>
+      </c>
+      <c r="E62" s="3">
         <v>24272400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18626600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18836400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17220100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17084400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17636100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16588600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15246700</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3064,17 +3209,20 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>318200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>369743200</v>
+      </c>
+      <c r="E66" s="3">
         <v>355404900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>341798200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>335111100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>333015100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>359497200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>383529600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>345534200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>353506200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>270019000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>282166000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>333314000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>375621000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>324041000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>303654000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12666200</v>
+      </c>
+      <c r="E72" s="3">
         <v>12470100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11277100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12389600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13233400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13867300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15292000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13417800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15977500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11210200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11146800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12265600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11788900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10331000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9572900</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23319200</v>
+      </c>
+      <c r="E76" s="3">
         <v>23178100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22149300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23685200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24001600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24366700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24660000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23743900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25886900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18804000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19846800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23097300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23025300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20855800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19049500</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2277500</v>
+      </c>
+      <c r="E81" s="3">
         <v>2275400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1096600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>698000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1177600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1384400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2016700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-906400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2065300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1615000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>966900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1917400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1956500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>974800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>104700</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>398800</v>
+      </c>
+      <c r="E83" s="3">
         <v>411700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>405500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>462100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>490200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>577300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>590900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>522700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>674000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>478100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>583500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>672900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>727900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>831700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>909200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5301500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4531700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>876900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5226800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7105400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6036300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-880200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3259300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4196500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8795900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9102000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-657000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4190000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4995000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2629400</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2225200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1268600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-963800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1287600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-916800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1083900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1921400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2879600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2685000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2108800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2386700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1786800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1963300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2472300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1650400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9426900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5667200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5870500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1754400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4884800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2332100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1677900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1015300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-528900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-795700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-174300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>105200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-945300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1458800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>89900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1130400</v>
+      </c>
+      <c r="E96" s="3">
         <v>751500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>397800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>430800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>582300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>690400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>542900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>428400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>661000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-288700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-608500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-471900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-475800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-133900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-262800</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>13181000</v>
+      </c>
+      <c r="E100" s="3">
         <v>11216800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6696300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9658500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9163200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6046400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7506400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6869300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3513700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14360500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7249900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1520100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2650800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6377800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7632600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>876200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-173800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1458600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1117500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1232700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>550500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-253500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>403800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-503800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>28600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-295400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>584400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>376400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>428800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-57100</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-671200</v>
+      </c>
+      <c r="E102" s="3">
         <v>844200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3161400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3794700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1594300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2872500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4694900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2998500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1715500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6331700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15882300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1487500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6271900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2412800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4970400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
